--- a/AutoAssign/gamesToAssign May 23-29.xlsx
+++ b/AutoAssign/gamesToAssign May 23-29.xlsx
@@ -2039,7 +2039,7 @@
         <v>47</v>
       </c>
       <c r="F27" t="s">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="G27" t="s">
         <v>52</v>
